--- a/gems-outputs/CC_セクション3.xlsx
+++ b/gems-outputs/CC_セクション3.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,10 +59,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -443,139 +445,139 @@
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>モジュール</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Claude Code講座</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>セクション3-動画1</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>動画タイトル</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>カスタムスラッシュコマンドによる定型作業の自動化</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>尺</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>8分</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>画面収録</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ゴール</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>自分だけのスラッシュコマンドを作成して定型作業を一発実行できるようになる</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>重要トピック</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>1. スラッシュコマンドの概念と仕組み  2. .claude/commandsディレクトリとmdファイルでの定義方法  3. プロジェクト用コマンドとグローバルコマンドの使い分け  4. $ARGUMENTSによる引数の受け渡し  5. コマンド化すべき作業の判断基準</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>受講者のつまずき</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>どんな作業をコマンド化すべきかの判断がつかない、mdファイルの書き方に戸惑う、引数の記法を間違える</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>画面操作方針</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>コマンド定義ファイルの作成・編集はエディタとClaude Code画面を並べてフルスクリーンで収録。実際にスラッシュコマンドが動く瞬間をゆっくり丁寧に見せる</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>位置付け方針</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>セクション3の1本目として、定型作業の自動化という核心的なテーマへの導入。スラッシュコマンドの即効性を体験させ、後続のSkills動画への橋渡しとする</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>参照一覧</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式ドキュメント（カスタムスラッシュコマンド解説）、.claude/commandsの仕様、プロンプトテンプレートの記法</t>
         </is>
@@ -609,216 +611,216 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>表紙</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>動画タイトルとセクション3の導入</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_表紙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>スラッシュコマンドの全体像</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>コマンドの仕組みと2種類の配置場所を図解で説明</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_全体像</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>コマンド化の判断基準</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>どんな作業をコマンド化すべきかの3基準を提示</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2:30</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_判断基準</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>$ARGUMENTS記法の解説</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>引数の受け渡し方法を図解</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_引数解説</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>セキュリティ注意点</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>コマンドファイルに書いてはいけない情報の整理</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>6:40</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_セキュリティ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>まとめ</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>学習ポイントの振り返りと次回予告</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_まとめ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ツール画面</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Claude Code＋エディタ画面</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>commandsディレクトリ作成・mdファイル編集・スラッシュコマンド実行の一連の流れを実演</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>3:00〜6:30</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_ツール画面</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>配布資料</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>コマンドテンプレート集</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>受講者がすぐにコピーして使えるmdファイルのひな形</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>動画説明欄に配置</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>CC_S3_01_テンプレート集</t>
         </is>
@@ -857,17 +859,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -882,24 +884,24 @@
           <t>セクション3へようこそ。このセクションのテーマは「業務自動化の武器を手に入れる」です。セクション2まで、Claude Codeの基本的な使い方や記憶の仕組みを学んでいただきました。このセクション3では、そこからもう一歩踏み込んで、同じ作業を何度も繰り返さなくて済む仕組みを一緒に作り上げていきます。</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>セクション概要</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>導入・セクション全体像</t>
         </is>
@@ -914,24 +916,24 @@
           <t>皆さん、毎日こんな経験をしていないでしょうか。「また同じ日報フォーマットを打ち込んでいる」「毎週月曜に同じ指示文をClaude Codeに入力している」「メール下書きを依頼するたびに、長い説明をしなければならない」。こういった定型的な作業は、一度自動化してしまえば、二度と手を止めずに済みます。そのための武器が、今日学ぶカスタムスラッシュコマンドです。この動画を最後まで見ていただければ、自分専用のスラッシュコマンドを作って、定型作業を一発実行できるようになります。さっそく始めましょう。</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V1企画骨子</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>1:15</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -946,24 +948,24 @@
           <t>まず、スラッシュコマンドとは何かを整理しましょう。</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式ドキュメント</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>1:15</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>2:30</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>スラッシュコマンドの概念</t>
         </is>
@@ -978,24 +980,24 @@
           <t>Claude Codeの入力欄でスラッシュ記号を入力すると、コマンドの候補が表示されるのを見たことがある方もいらっしゃるかもしれません。あの仕組みを自分でカスタマイズできるのが、カスタムスラッシュコマンドです。仕組みはとてもシンプルです。プロジェクトフォルダの中に「.claude」というフォルダがあります。その中の「commands」というフォルダに、Markdownファイルを置くだけです。そのMarkdownファイルの名前が、そのままコマンド名になります。たとえば「daily-report.md」というファイルを作れば、Claude Codeの入力欄で「/daily-report」と入力するだけで、そのファイルに書かれたプロンプトが自動的に実行されます。毎回同じ長い指示を入力する必要はありません。コマンド名だけで、すべてが動き出します。配置場所については2種類あります。プロジェクトフォルダ内の「.claude/commands」に置くと、そのプロジェクト限定で使えるコマンドになります。一方、ホームディレクトリの「~/.claude/commands」に置くと、どのプロジェクトでも横断的に使えるコマンドになります。チームで共有したいコマンドはプロジェクト側、自分だけが使う個人用コマンドはホーム側に置く、という使い分けが推奨されています。</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式ドキュメント（カスタムスラッシュコマンド解説）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2:30</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>2:45</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -1010,24 +1012,24 @@
           <t>さて、「どんな作業をコマンド化すればいいの？」という疑問が浮かぶかもしれません。判断基準をお伝えします。</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2:45</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>3:00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>コマンド化の判断基準</t>
         </is>
@@ -1042,24 +1044,24 @@
           <t>コマンド化すべき作業の判断基準は、大きく3つあります。1つめは、繰り返し頻度が高い作業です。週2回以上行っている作業は、コマンド化の有力候補です。毎日の日報、毎週の進捗報告、定期的なメール下書きなど、思い当たる作業がある方は多いのではないでしょうか。2つめは、出力フォーマットを統一したい作業です。日報や議事録、メール下書きなど、決まった形式で出力したい場合は、コマンドにフォーマットを組み込んでおけば、毎回同じ品質の成果物が得られます。3つめは、複数のステップをまとめて一度に実行したい作業です。たとえば「ファイルを読み込んで、要約して、特定のフォーマットで出力する」という一連の処理を、コマンド一つで完了させることができます。</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報（コマンド化すべき作業の3つの判断基準）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>3:00</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>3:15</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -1074,24 +1076,24 @@
           <t>では、実際にコマンドを作ってみましょう。画面を見ながら一緒に進めていきましょう。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>S3-V1企画骨子</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>3:15</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>実演①：commandsディレクトリ作成とmdファイル作成</t>
         </is>
@@ -1106,24 +1108,24 @@
           <t>まずはターミナルを開いて、プロジェクトフォルダの中に「.claude/commands」というディレクトリを作ります。「mkdir -p .claude/commands」というコマンドを入力してください。「mkdir」はディレクトリを作るコマンドで、「-p」は中間のフォルダも自動で作ってくれるオプションです。はい、できましたね。次に、エディタを開いてこのフォルダの中に「daily-report.md」というファイルを作成します。ファイルの中には、日報を作るためのプロンプトを書きます。たとえば「今日の業務内容を箇条書きで教えてください。以下のフォーマットで日報を作成してください」という指示と、その後に日報のテンプレートを貼り付けます。日付、担当者名、業務内容、明日の予定、所感、という項目を含めたテンプレートです。ファイルを保存したら、Claude Codeに戻ります。入力欄にスラッシュを入力すると、今作った「daily-report」がコマンドの候補として表示されているはずです。試してみましょう。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式ドキュメント（カスタムスラッシュコマンド解説）</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>5:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>実演②：コマンドの実行確認</t>
         </is>
@@ -1138,24 +1140,24 @@
           <t>入力欄に「/daily-report」と入力してEnterを押します。すると、先ほどファイルに書いたプロンプトが自動的に実行されます。ご覧ください。日報の出力が始まりました。毎回同じ長い指示を書かなくても、このコマンド一つで完了です。ファイルを1つ置いただけで、これだけのことが自動化できます。「思ったより簡単だな」と感じていただけたのではないでしょうか。実は、これが一番大切なポイントです。難しいプログラムを書く必要は一切ありません。Markdownファイルに普通の文章を書くだけで、自分専用のコマンドが完成します。</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式ドキュメント</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>5:00</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -1170,24 +1172,24 @@
           <t>基本的なコマンドの作り方は理解していただけましたか。次に、もう少し便利な使い方として、引数の受け渡しについて説明します。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>6:40</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>$ARGUMENTSによる引数の受け渡し</t>
         </is>
@@ -1202,24 +1204,24 @@
           <t>コマンドファイルの中で「$ARGUMENTS」という変数を使うと、コマンド実行時に文字を追加して差し込むことができます。具体的に説明しましょう。たとえば「meeting-summary.md」というコマンドファイルを作るとします。ファイルの中に「$ARGUMENTSの内容をもとに、以下のフォーマットで議事録を作成してください」という指示を書きます。このコマンドを実行するとき、「/meeting-summary 2024年度第4回定例会議」のように後ろに文字を追加すると、「$ARGUMENTS」の部分に「2024年度第4回定例会議」という文字が差し込まれます。同じコマンドを、異なる会議名や条件で使い回すことができるわけです。一つのコマンドで複数のバリエーションに対応できるので、コマンドファイルの数を増やさなくて済みます。最初のうちは$ARGUMENTSを使わない単純なコマンドから始めて、慣れてきたら引数を活用するという順番でステップアップしていただければ十分です。</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報（$ARGUMENTSによる引数の受け渡し）</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>6:40</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>6:50</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -1234,24 +1236,24 @@
           <t>便利なスラッシュコマンドですが、使うにあたって一点だけ、重要な注意事項をお伝えします。</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>6:50</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>セキュリティ注意点</t>
         </is>
@@ -1266,24 +1268,24 @@
           <t>コマンドファイルには、APIキーやパスワードなどの機密情報を直接書かないようにしてください。特に、プロジェクトフォルダ側の「.claude/commands」はGit管理の対象になる場合があります。GitHubにプッシュした瞬間に、チームメンバーや場合によっては外部の方からも見えてしまうリスクがあります。機密情報が必要な場合は、環境変数として設定しておき、コマンドファイルの中では環境変数名だけを参照するようにしてください。個人用のコマンドは「~/.claude/commands」に置くのが安全です。こちらはGit管理の対象外になりますし、チームメンバーには見えません。この点だけはしっかり押さえておいてください。意識するのはこの1点だけで、あとは自由にカスタムコマンドを作り込んでいただけます。</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報（セキュリティ上の注意）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>7:30</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -1298,24 +1300,24 @@
           <t>では、この動画のまとめに入ります。</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>S3-V1企画骨子</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>7:30</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>7:50</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>まとめ</t>
         </is>
@@ -1330,24 +1332,24 @@
           <t>今日学んだポイントを整理します。カスタムスラッシュコマンドは、「.claude/commands」にMarkdownファイルを置くだけで作成できます。ファイル名がそのままコマンド名になります。プロジェクト用とグローバル用の2か所に置けます。「$ARGUMENTS」を使えば引数を受け渡して、同じコマンドを使い回せます。そしてAPIキーなど機密情報はファイルに書かず、環境変数で管理します。定型作業をコマンド化するかどうかの判断基準は、「週2回以上行っているか」「フォーマットを統一したいか」「複数ステップを一度に実行したいか」の3点です。これらに当てはまる作業があれば、積極的にコマンド化してみてください。</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>S3-V1参照情報</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>7:50</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>クロージング・次回予告</t>
         </is>
@@ -1362,7 +1364,7 @@
           <t>次の動画では、今日のスラッシュコマンドと似ているようで少し異なる、「Agent Skills」という仕組みを学びます。スラッシュコマンドが「ユーザーが明示的に呼び出す」ものだとすれば、Skillsは「Claudeが状況を読んで自動的に参照する」仕組みです。より高度な自動化の第一歩として、ぜひ次の動画もご覧ください。皆さんの学習を応援しています。次の動画でお会いしましょう。</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V2企画骨子</t>
         </is>
@@ -1386,238 +1388,238 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>カスタムスラッシュコマンドの概念をブラウザAIとの対比で分かりやすく説明する</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>「毎回同じ長い指示を書かなくてよくなる」という実感を持てる具体例で導入する</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>.claude/commandsとそのファイル構造を図解とともに正確に説明する</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>プロジェクト用とグローバル用の2種類の配置場所を、使い分けの理由とともに説明する</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>コマンド化すべき作業の3基準（頻度・フォーマット統一・複数ステップ）を実例つきで提示する</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>受講者が「自分の日常業務のどれをコマンド化すべきか」をすぐに判断できるよう具体例を豊富に用意する</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>実演：「.claude/commands」ディレクトリ作成からmdファイル作成・コマンド実行まで通しで見せる</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>操作の速さを調整し、初心者でも追いつけるペースで説明する。コマンドが実行される瞬間を分かりやすく強調する</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>$ARGUMENTS変数の使い方を、具体的なコマンド例（議事録作成コマンドなど）で説明する</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>「最初は使わなくてよい、慣れたら活用する」という段階的なアドバイスを添える</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>セキュリティ上の注意（機密情報を直接書かない）を具体的なリスクとともに伝える</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>リスクだけで終わらず「環境変数で管理する」という代替手段を必ずセットで提示する</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>次回のAgent Skills動画との違いを簡潔にプレビューし、継続視聴を促す</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>「呼び出す」vs「自動的に参照する」という対比を使ってスラッシュコマンドとの違いを予告する</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>スライドとツール画面の切り替えタイミングを確認し、視聴者の混乱を防ぐ</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>切替の際に毎回「画面を切り替えます」「スライドに戻ります」という声の案内を入れる</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>「Markdownファイルを1つ置くだけ」というシンプルさを複数回強調する</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>心理的なハードルを下げることを意識し、「難しくない」というメッセージを繰り返す</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>8分の尺に対して10000〜11200字の増量モード目標を意識した話速・ポーズ配分を調整する</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>実演中の説明を特に丁寧に行い、操作の意味を一つひとつ言葉にすることで文字数と情報量を両立させる</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>「ご覧ください」「確認できましたか」などの確認フレーズを実演パートに入れる</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>画面収録中は視聴者が迷子にならないよう、現在地の案内を頻繁に行う</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>丁寧語・断定しない表現の一貫性を確認する</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>「〜です」「〜になります」「〜かもしれません」という語調で統一し、高圧的にならないよう注意する</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>スライド「コマンド化の判断基準」で受講者の日常業務に即した具体例を豊富に挙げる</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>日報・議事録・メール下書き・週次レポートなど、ビジネス現場で誰もが経験する作業を選ぶ</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>全14講師アクション（表情・ジェスチャー・話速・スライド操作・視線等）の演出指示を確認する</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>各sceneのdirectionフィールドに演出指示が記載されていることを最終確認する</t>
         </is>
@@ -1651,139 +1653,139 @@
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>モジュール</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Claude Code講座</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>セクション3-動画2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>動画タイトル</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Agent Skills（SKILL.md）の基礎：Claudeに「やり方」を教える</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>尺</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>画面収録</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ゴール</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdを書いてClaudeに特定の作業手順を教え、再現性の高い出力を得られるようになる</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>重要トピック</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>1. コマンドとSkillsの違い  2. SKILL.mdの4パート構造  3. Claudeに作らせるSKILL.md生成テクニック  4. 公式skill-creatorの使い方  5. 1日1回の繰り返し作業をスキル化する発想</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>受講者のつまずき</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>コマンドとSkillsの違いがわからず混乱する、SKILL.mdの記述量が多くて挫折する、どこまで詳細に書けばよいかの判断がつかない</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>画面操作方針</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの作成・編集はエディタをフルスクリーンで収録。skill-creatorの起動から完成までの対話を丁寧にゆっくり見せる。コマンドとSkillsの違いを図解スライドで明確に示す</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>位置付け方針</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>セクション3の2本目として、前回のスラッシュコマンドより高度な「Claudeへの作業手順の教え込み」を実現する。後続の実践動画（V3）への橋渡しとなる基礎固め動画</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>参照一覧</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式ドキュメント（Agent Skills解説）、SKILL.mdの仕様と記法、公式skill-creatorの使い方</t>
         </is>
@@ -1817,189 +1819,189 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>表紙</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>動画タイトルとセクション3-2の導入</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_表紙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>コマンドとSkillsの違い</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2つの仕組みの違いを図解で比較</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_比較図</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの4パート構造</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>スキルファイルの構成要素を図解で説明</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2:20</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_構造図</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>スキル化の候補一覧</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>毎日繰り返す作業のリストを提示し、スキル化の発想を広げる</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_候補一覧</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>まとめ</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>学習ポイントの振り返りと次回予告</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>9:10</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_まとめ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>ツール画面</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>エディタ＋Claude Code画面</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの手書き作成とskill-creatorを使った自動生成を実演</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>3:30〜8:10</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_ツール画面</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>配布資料</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdテンプレート</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>受講者がすぐに転用できる4パート構造のひな形</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>動画説明欄に配置</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CC_S3_02_テンプレート</t>
         </is>
@@ -2038,17 +2040,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2063,24 +2065,24 @@
           <t>前回の動画では、カスタムスラッシュコマンドを使って定型作業を一発実行する方法を学びました。今回はそこからもう一歩踏み込んで、Claudeに「作業のやり方そのもの」を教える方法、「Agent Skills」についてお話しします。</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V2企画骨子</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>今回の動画の概要</t>
         </is>
@@ -2095,24 +2097,24 @@
           <t>前回のスラッシュコマンドも今回のAgent Skillsも、どちらも「Claudeの動き方をカスタマイズする」という点では共通しています。ただ、役割が違います。今日の動画では、まずこの2つの違いをはっきりさせたうえで、SKILL.mdという設定ファイルの書き方を学びます。そして、SKILL.md自体をClaudeに自動生成させるテクニックと、公式の「skill-creator」という便利な機能もご紹介します。最後まで見ていただければ、Claudeを自分専用のAIアシスタントに育てていく第一歩が踏み出せます。</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>S3-V2企画骨子（学習ゴール）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2127,24 +2129,24 @@
           <t>まず、コマンドとSkillsの違いを確認しましょう。</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>2:20</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>コマンドとSkillsの違い</t>
         </is>
@@ -2159,24 +2161,24 @@
           <t>スラッシュコマンドは、「ユーザーが明示的に呼び出す」仕組みです。「/daily-report」と入力したとき、そのタイミングで初めてコマンドが動きます。Claudeは待っていて、呼ばれたら動く、という関係です。一方、Agent Skillsは違います。Claudeが「あ、これはスキルを使うべき状況だ」と自分で判断して、自動的に参照する仕組みです。たとえば「コードをレビューしてください」とメッセージを送ったとき、Claudeはコードレビュー用のSKILL.mdを自動的に参照して、そこに書かれた手順に従って動きます。ユーザーは何も特別な操作をしなくて済みます。配置場所の違いもあります。コマンドは「.claude/commands」フォルダにMarkdownファイルを置きますが、スキルは「.claude」ディレクトリの直下に「SKILL.md」というファイルを置きます。整理すると、コマンドは「呼び出して使う単発の指示実行」、Skillsは「Claudeが状況に応じて自動参照する複雑な作業手順書」という違いです。どちらが優れているというものではなく、使い分けることで最大限の効果が出ます。</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報（コマンドとスキルの違い）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2:20</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>2:30</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2191,24 +2193,24 @@
           <t>違いが分かったところで、SKILL.mdの書き方を見ていきましょう。</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2:30</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>3:30</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの4パート構造</t>
         </is>
@@ -2223,24 +2225,24 @@
           <t>SKILL.mdは、4つのパートで構成されています。1つめは「スキルの名前と説明」です。このスキルが何をするものか、Claudeが正しく判断できるよう、分かりやすく書きます。2つめは「トリガー条件」です。どのような状況や依頼があったときに、このスキルを発動すべきかを書きます。たとえば「コードのレビューを求められたとき」「日報の作成を依頼されたとき」のように、具体的な条件を書くほどClaudeが正確に判断できます。3つめは「実行手順」です。Claudeが従うべき具体的なステップを書きます。「まず〇〇を確認する」「次に〇〇の観点でチェックする」という形で、細かく記載するほど再現性が高まります。4つめは「出力ルール」です。成果物の形式や品質基準を書きます。「箇条書きで3点以内にまとめる」「日本語で出力する」のように、アウトプットの仕様を明記します。特に3番目の実行手順と4番目の出力ルールは、具体的に書けば書くほど、毎回同じクオリティの成果物が得られます。最初はこの4パートを意識して書いてみるだけで、大きく違いが出ます。</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報（SKILL.mdの4パート構造）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>3:30</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>3:45</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2255,24 +2257,24 @@
           <t>では実際にSKILL.mdを作ってみましょう。最初は手で書く方法を確認します。</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>S3-V2企画骨子</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>3:45</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>実演①：SKILL.mdの手作成</t>
         </is>
@@ -2287,24 +2289,24 @@
           <t>エディタを開いて、「.claude」フォルダの中に「SKILL.md」というファイルを新規作成します。では、日報作成スキルを作ってみます。まず1つめのパート、スキルの名前と説明から書きます。「スキル名：日報作成」、「説明：その日の業務内容をもとに、決められたフォーマットで日報を作成するスキル」と書きます。次に2つめのパート、トリガー条件です。「ユーザーが日報の作成を依頼したとき」「今日の業務をまとめてほしいと言われたとき」と書きます。このように、どんな言葉で依頼されてもトリガーされるよう、複数のパターンを書いておくと安心です。3つめのパート、実行手順です。「手順1：ユーザーに今日行った業務の内容を3〜5点で教えてもらう。手順2：業務内容をカテゴリ別（企画、対応、確認等）に分類する。手順3：明日の予定を確認する。手順4：全体の所感を1〜2文で書く。手順5：以下の出力ルールに従って日報を生成する」という形で書きます。最後に4つめのパート、出力ルールです。フォーマットそのものをテンプレートとして貼り付けます。「日付：」「氏名：」「業務内容：」「明日の予定：」「所感：（3行以内）」という構造をそのまま書いておきます。これで4パートが揃いました。保存して、Claude Codeに戻ります。「日報を作ってください」と入力すると、先ほど書いた手順に沿って、業務内容を聞いてくれます。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報（SKILL.mdの4パート構造）</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>5:45</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2319,24 +2321,24 @@
           <t>ここまでは手で書く方法を見ていただきました。ただ、SKILL.mdを一から書くのは、最初は少し大変に感じるかもしれません。そこで便利な方法を2つご紹介します。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>5:45</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>7:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>テクニック：Claudeに作らせるSKILL.md</t>
         </is>
@@ -2351,24 +2353,24 @@
           <t>1つめの方法は、SKILL.mdの作成自体をClaudeに依頼する方法です。Claude Codeの入力欄に「日報作成スキルのSKILL.mdを作ってください。4パート構造で書いてください」と入力するだけで、Claudeが自動的にSKILL.mdの内容を生成してくれます。実際に試してみます。入力します。するとClaudeが4パートを意識したSKILL.mdの内容を書いてくれました。「なかなかいい内容ですね」ただし、このまま使うのではなく、必ず中身を確認してください。特に確認すべきポイントは2つです。まず「トリガー条件」が、自分の使い方に合っているかどうかです。次に「出力ルール」に、自分が使いたいフォーマットが正確に反映されているかどうかです。この2点を自分の業務に合わせて微調整するだけで、かなり実用的なスキルになります。生成して、確認して、微調整する。このサイクルが大切です。</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報（SKILL.md自体をClaudeに作らせるテクニック）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>7:00</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>8:10</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>実演②：公式skill-creatorの使い方</t>
         </is>
@@ -2383,24 +2385,24 @@
           <t>2つめの方法は、Anthropicが公式に提供している「skill-creator」という機能です。Claude Codeの入力欄で「/skill-creator」と入力すると起動します。試してみます。起動しました。「どのようなスキルを作りたいですか？」と質問が来ました。対話形式で質問に答えていくだけで、最適なSKILL.mdが自動的に完成します。たとえば「メールの下書きを作るスキルです」と答えると、次に「どのような種類のメールに対応しますか？」「相手はどのような立場の方ですか？」「メールの口調はどうしますか？」といった具体的な質問が続きます。これに答えていくだけで、カスタマイズされたSKILL.mdが完成します。初めてスキルを作る方は、手で書くより先にこのskill-creatorから始めるのが最も取り組みやすい方法です。ガイドに従って質問に答えるだけですので、「何を書けばいいか分からない」という迷いが解消されます。生成されたSKILL.mdは「.claude」フォルダに自動的に保存されますので、あとは中身を確認して微調整するだけです。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報（公式skill-creator）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>8:10</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2415,24 +2417,24 @@
           <t>スキルの作り方が分かったところで、「どんな作業をスキル化すればよいか」について少し考えてみましょう。</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>9:10</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>1日1回やることはスキル化する発想</t>
         </is>
@@ -2447,24 +2449,24 @@
           <t>スキル化の有力候補は「1日1回以上やっていること」です。日報の作成はすでに例として挙げましたが、他にもこんな作業が対象になります。朝のメールチェック後に重要事項を要約するスキル。毎日のタスクリストを優先順位順に並べ替えるスキル。会議終了後に議事録をまとめるスキル。コードを書いたあとに簡単なレビューをかけるスキル。どれも毎日繰り返していることですよね。これらを一度スキルとして定義しておけば、翌日から同じクオリティの成果物が毎回得られます。Claude Codeを自分専用のAIアシスタントに育てていく、その積み重ねがスキル化なのです。最初は1つだけでも構いません。まず「1日1回は必ずやっていること」を1つ選んで、スキルを作ってみてください。</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報（1日1回やることはスキル化するという発想）</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>9:10</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -2479,24 +2481,24 @@
           <t>では、この動画のまとめをお伝えします。</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>S3-V2企画骨子</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>9:45</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>まとめ</t>
         </is>
@@ -2511,24 +2513,24 @@
           <t>今日学んだポイントをまとめます。コマンドは「呼び出して使う」、Skillsは「Claudeが状況を読んで自動参照する」という違いがあります。SKILL.mdは「名前と説明」「トリガー条件」「実行手順」「出力ルール」の4パート構造で書きます。SKILL.mdはClaudeに自動生成させるか、公式skill-creatorを使うと楽に作れます。生成後は必ずトリガー条件と出力ルールを確認して、自分の業務に合わせて微調整します。スキル化の有力候補は「1日1回以上行っている作業」です。そして、一度作ったら終わりではなく「作って、試して、直す」というサイクルを繰り返すことで、スキルの精度はどんどん上がっていきます。</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>S3-V2参照情報</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>9:45</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>クロージング・次回予告</t>
         </is>
@@ -2543,7 +2545,7 @@
           <t>次の動画では、今日学んだSKILL.mdの知識を使って、実際に2つのスキルを一緒に作ります。「特定のフォーマットで資料を出力するスキル」と「コードをチェックするスキル」です。作るだけでなく、テストして改善するサイクルも体験できます。ぜひ楽しみにしていてください。皆さんの学習を応援しています。次の動画でお会いしましょう。</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V3企画骨子</t>
         </is>
@@ -2567,238 +2569,238 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>コマンドとSkillsの違いを「呼び出す」vs「自動参照」という対比で明確に説明する</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>図解スライドを使い、どちらが優れているのではなく「使い分けが大切」という結論を示す</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの4パート構造（名前と説明・トリガー条件・実行手順・出力ルール）を図解とともに説明する</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>特に「実行手順と出力ルールを具体的に書くほど再現性が高まる」という点を強調する</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>実演①：SKILL.mdを4パートに沿って手で書きながら説明する</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>各パートを書くたびに「なぜこれが必要か」を口頭で補足し、受講者が後で自分で書けるよう解説する</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>テクニック：「SKILL.mdの作成をClaudeに依頼する」方法を実演する</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>生成後に必ずトリガー条件と出力ルールを確認・微調整するという手順をセットで伝える</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>公式skill-creatorの起動（/skill-creator）から完成までの対話フローを実演する</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>「初めての方はこちらから」という案内を添えて、ハードルを下げる言葉を選ぶ</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>「1日1回やることはスキル化する」という発想を具体例とともに伝える</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>日報・議事録・メール要約・タスク整理など、誰もが共感できる日常業務を例示する</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>「作って、試して、直す」という改善サイクルを繰り返すことの重要性を伝える</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>最初から完璧を目指さず、動くものを作ってから磨くアプローチを推奨する</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>次の実践動画（V3）への橋渡しを明確に行う</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>V3で作る2つのスキル（フォーマット出力・コードチェック）を具体的に予告して継続視聴を促す</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>スライドとツール画面の切り替えタイミングに声の案内を入れる</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>「画面を切り替えます」「スライドに戻ります」という案内を毎回入れて視聴者を迷わせない</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>10分の尺に対して12400〜14000字の増量モード目標を意識した話速・ポーズ配分を調整する</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>実演中に操作の意味を一つひとつ言葉にすることで文字数と情報量を両立させる</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>「コマンドとSkillsを混同しやすい」というつまずきポイントへの対処を丁寧に行う</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>違いの説明を2回以上繰り返し、図解と口頭の両方で確実に理解してもらう</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>丁寧語・断定しない表現の一貫性を確認する</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>「〜です」「〜になります」「〜かもしれません」という語調で統一する</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>skill-creatorの対話フローで「どんな質問が来るか」を事前にシミュレーションしておく</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>実演中に予想外の質問が来ても慌てないよう、事前に複数回テストしておく</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>全14講師アクション（表情・ジェスチャー・話速・スライド操作・視線等）の演出指示を確認する</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>各sceneのdirectionフィールドに演出指示が記載されていることを最終確認する</t>
         </is>
@@ -2832,139 +2834,139 @@
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>モジュール</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Claude Code講座</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>セクション3-動画3</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>動画タイトル</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>実践：特定のフォーマットで資料を出力させる・コードをチェックするスキル</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>尺</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>画面収録</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ゴール</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>実務で使えるスキルを2つ作成し、テストと改善のサイクルを体験する</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>重要トピック</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>1. フォーマット統一スキルの設計ポイント  2. 具体的なテンプレートの書き方  3. コードレビュースキルの5観点と優先順位  4. テスト・評価・修正の3ステップ改善サイクル  5. プロンプト記述の3つのコツ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>受講者のつまずき</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>プロンプトの書き方が曖昧で出力が安定しない、コードレビューの観点が思いつかない、改善ポイントの見つけ方がわからない</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>画面操作方針</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの作成・テスト・改善の一連の流れをエディタとClaude Code画面を並べてフルスクリーンで収録。出力が期待通りでないシーンもあえて見せて、改善プロセスを体感させる</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>位置付け方針</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>セクション3の3本目として、前回のSkills基礎を踏まえて実際に2つのスキルを作り上げる実践動画。「作って試して直す」サイクルを体験させる</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>参照一覧</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの実践パターン、フォーマット定義のベストプラクティス、コードレビュー観点の標準リスト</t>
         </is>
@@ -2998,216 +3000,216 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>表紙</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>動画タイトルとセクション3-3の導入</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_表紙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>フォーマット統一スキルの設計ポイント</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>安定した出力のためのテンプレート設計の考え方を提示</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_フォーマット設計</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>コードレビュースキルの5観点</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>レビュー観点と優先順位を一覧表で提示</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_レビュー観点</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>テスト・評価・修正サイクル</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>3ステップ改善サイクルのフロー図を示す</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>7:30</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_改善サイクル</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>プロンプト記述の3つのコツ</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>安定した出力を得るためのプロンプト作成の実践テクニック</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_プロンプトコツ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>まとめ</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>学習ポイントの振り返りと次回予告</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_まとめ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ツール画面</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>エディタ＋Claude Code画面</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>フォーマット統一スキルとコードレビュースキルの作成・テスト・改善を実演</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>1:30〜7:20</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_ツール画面</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>配布資料</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>コードレビュー観点チェックシート</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>受講者が自分のSKILL.mdに組み込める観点リスト</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>動画説明欄に配置</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>CC_S3_03_レビューチェックシート</t>
         </is>
@@ -3246,17 +3248,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3271,24 +3273,24 @@
           <t>前回の動画では、SKILL.mdの4パート構造と、Claudeに作らせるテクニックを学びました。今回はそれを使って、実際に2つのスキルを一緒に作り上げましょう。</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V3企画骨子</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>今回の動画の概要</t>
         </is>
@@ -3303,24 +3305,24 @@
           <t>今日作るスキルは2つです。1つめは「特定のフォーマットで資料を出力させるスキル」です。日報や議事録など、決まった形式で出力させたいときに使います。2つめは「コードをチェックするスキル」です。書いたコードをClaudeに自動でレビューしてもらう仕組みです。この2つを作るだけでなく、「テストして改善する」サイクルも体験していただきます。最初から完璧なスキルができるわけではありません。作って試して、気になる点を直す。この繰り返しがスキルの精度を上げる近道です。ではさっそく始めましょう。</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>S3-V3企画骨子（学習ゴール）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3335,24 +3337,24 @@
           <t>まず、フォーマット統一スキルの設計ポイントからお伝えします。</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>1:30</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>フォーマット統一スキルの設計ポイント</t>
         </is>
@@ -3367,24 +3369,24 @@
           <t>フォーマット統一スキルで最も大切なのは、「出力ルール」の中に具体的なテンプレートを定義することです。「日報を作って」という指示だけでは、Claudeは毎回異なる形式で出力します。ある日は箇条書き、ある日は文章形式、ある日は表形式。これでは「フォーマットを統一する」というスキルの目的が果たせません。解決策は、テンプレートをそのままSKILL.mdの出力ルールに貼り込んでしまうことです。さらに、各項目に「何を書くべきか」の説明も添えると品質が安定します。たとえば「所感は3行以内で、具体的な気づきや改善点を含めること」のように、数値と内容の両方を指定します。</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（フォーマット統一スキルの設計ポイント）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>1:30</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>1:45</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3399,24 +3401,24 @@
           <t>では実際にフォーマット統一スキルを作ってみましょう。</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>S3-V3企画骨子</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>1:45</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>4:00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>実演①：フォーマット統一スキルの作成とテスト</t>
         </is>
@@ -3431,24 +3433,24 @@
           <t>エディタを開いて、日報作成スキルのSKILL.mdを書いていきます。トリガー条件は「日報の作成を依頼されたとき」「今日の業務をまとめてほしいと言われたとき」とします。実行手順は「まず業務内容を3〜5点で確認する、次に各業務をカテゴリ別に整理する、最後に出力ルールのフォーマットで出力する」という3ステップです。そして出力ルール、ここが最重要です。テンプレートをそのまま貼り込みます。「日付：YYYY-MM-DD」「担当者：」「本日の業務：（カテゴリ：内容の形式で記載）」「明日の予定：（最大3件）」「所感：（3行以内、具体的な気づきか改善点を必ず1つ含める）」という形です。保存したら、Claude Codeで試します。「今日の日報を作ってください」と入力します。Claudeが業務内容を確認してきます。「提案書の作成と、お客様対応、チームミーティングです」と答えると、フォーマット通りの日報が出てきました。いい感じです。ただ、所感が少し抽象的ですね。「良い一日でした」という内容ではなく、「具体的な気づきを含めてほしい」という部分が守られていません。これを修正していきましょう。</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（フォーマット統一スキルの設計ポイント）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>4:00</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SKILL.mdの微調整と再テスト</t>
         </is>
@@ -3463,24 +3465,24 @@
           <t>エディタに戻って、所感の説明を修正します。「所感：（3行以内、抽象的な感想は書かない。今日の業務で気づいた課題か改善点を1つ以上、具体的に書くこと）」というように、禁止事項と要件をより明確にします。保存して再テストします。今度は「今日のお客様対応を通じて、質問への回答速度に改善の余地があることに気づきました」という具体的な内容が出てきました。こんなふうに、「どこが足りないか」を言語化してSKILL.mdに反映するだけで、出力の品質がぐっと上がります。3回ほど繰り返すと、かなり実用的な品質になります。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（テスト・評価・修正の3ステップ改善サイクル）</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>4:45</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3495,24 +3497,24 @@
           <t>では次に、コードレビュースキルを作っていきます。まずレビューの観点を整理しておきましょう。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>4:45</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>コードレビュースキルの5観点</t>
         </is>
@@ -3527,24 +3529,24 @@
           <t>コードレビュースキルで大切なのは、観点に優先順位をつけることです。観点が多すぎると、些細な指摘に埋もれて重要な問題が見落とされてしまいます。コードレビューの観点は5つ、優先順位の高い順に並べています。1番目は「動作の正確性」です。コードが意図通りに動くかどうかの確認です。2番目は「セキュリティ」です。APIキーのハードコードや、インジェクションのリスクなど、安全性に関わる問題です。3番目は「可読性」です。変数名や関数名が分かりやすいか、コメントが適切かの確認です。4番目は「パフォーマンス」です。無駄なループや重い処理がないかの確認です。5番目は「エラーハンドリング」です。例外処理が適切に実装されているかの確認です。この優先順位をSKILL.mdに明記しておくと、Claudeは優先度の高い問題を先に報告してくれます。なお、Claudeのレビュー結果はあくまで「見落とし防止の補助ツール」として活用してください。最終的な判断は皆さん自身が行うことが重要です。</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（コードレビュースキルの5つの観点と優先順位）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>5:45</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3559,24 +3561,24 @@
           <t>では実際にコードレビュースキルを作って試してみましょう。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>S3-V3企画骨子</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>5:45</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>実演②：コードレビュースキルの作成とテスト</t>
         </is>
@@ -3591,24 +3593,24 @@
           <t>エディタに戻って、SKILL.mdにコードレビュースキルを追加します。トリガー条件は「コードのレビューを依頼されたとき」「このコードを確認してほしいと言われたとき」とします。実行手順は「コードの目的と言語を確認する、次に5つの観点を優先順位の高い順にチェックする、最後に問題のある箇所を観点と理由とともに報告する」という流れです。出力ルールは「問題点は優先度順に箇条書きで報告すること。各指摘には観点・場所・理由・修正提案を含めること。問題がない観点は『問題なし』と明記すること」と書きます。保存して試してみましょう。サンプルとして、APIキーがハードコードされているPythonコードを貼り付けます。「このコードをレビューしてください」と入力します。まずセキュリティの問題として「APIキーがソースコードに直接書かれています。環境変数に移動してください」という指摘が1番目に来ました。次に動作の正確性として「エラーハンドリングがありません」という指摘が続きます。優先順位通りに報告されていますね。これだけで、人間のコードレビューでよく見落とすポイントを自動でチェックできます。</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（コードレビュースキルの5つの観点と優先順位）</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>7:30</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3623,24 +3625,24 @@
           <t>ここまで2つのスキルを作ってテストしました。次に、改善サイクルについて整理しておきましょう。</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>7:30</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>テスト・評価・修正の3ステップ改善サイクル</t>
         </is>
@@ -3655,24 +3657,24 @@
           <t>スキルを作ったあとの改善サイクルは、3つのステップです。まず「テスト」です。複数パターンの業務データで試してみます。日報スキルであれば、業務内容が多い日、少ない日、種類が偏っている日など、いくつかのパターンで試します。コードレビュースキルであれば、問題があるコードと問題がないコードの両方を試します。次に「評価」です。期待していた出力と実際の出力の違いを具体的に言語化します。「所感が抽象的すぎる」「優先度の低い指摘が先に出てくる」など、どこがずれているかを明確にします。そして「修正」です。評価で見つけた問題点をSKILL.mdに反映します。出力ルールの文言を変える、禁止事項を追加する、手順をより細かく書くなどの調整を行います。このサイクルを3回ほど繰り返すと、かなり実用的な品質になります。最初から完璧を目指す必要はありません。「まず動くものを作って、使いながら磨く」というアプローチが一番効果的です。</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（テスト・評価・修正の3ステップ改善サイクル）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>8:40</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3687,24 +3689,24 @@
           <t>最後に、安定した出力を得るためのプロンプト記述のコツを3つお伝えします。</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>8:40</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>プロンプト記述の3つのコツ</t>
         </is>
@@ -3719,24 +3721,24 @@
           <t>安定した出力を得るためのプロンプト記述のコツは3つあります。1つめは「良い例と悪い例を両方書く」ことです。良い出力の例だけを示すより、悪い例も「こういう出力は不要」と明記することで、Claudeが出力の方向性をより正確に理解できます。2つめは「数値で基準を示す」ことです。「簡潔に書く」という指示は人によって解釈が変わります。「3行以内で書く」「最大5点まで列挙する」のように数値で具体的に示すと、ブレが大幅に減ります。3つめは「禁止事項を明記する」ことです。「抽象的な表現は使わない」「コードを省略しない」「英語で出力しない」など、意図しない出力を防ぐための禁止事項を書き添えておくと、出力の安定性が格段に上がります。この3つを意識するだけで、SKILL.mdの品質は大きく変わります。ぜひ試してみてください。</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報（プロンプト記述の3つのコツ）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>9:30</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -3751,24 +3753,24 @@
           <t>では、この動画のまとめをお伝えします。</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>S3-V3企画骨子</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>9:30</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>9:50</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>まとめ</t>
         </is>
@@ -3783,24 +3785,24 @@
           <t>今日学んだポイントをまとめます。フォーマット統一スキルでは、出力ルールに具体的なテンプレートを貼り込み、各項目に説明を添えることが安定出力の鍵です。コードレビュースキルでは、観点に優先順位をつけて重要な問題が埋もれないようにします。改善サイクルはテスト・評価・修正の3ステップで、3回繰り返すと実用的な品質になります。プロンプト記述のコツは、良い例と悪い例を併記する、数値で基準を示す、禁止事項を明記する、の3点です。最初から完璧を目指さず、「動くものを作ってから磨く」アプローチが一番続けやすい方法です。</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>S3-V3参照情報</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>9:50</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>クロージング・次回予告</t>
         </is>
@@ -3815,7 +3817,7 @@
           <t>次の動画は、セクション3の最後として「外部ツールとの連携」を学びます。MCPという仕組みを使って、Claude Codeとfreeeやブラウザなどのツールをつなぐことができます。今日のスキル作成でClaudeを育てた経験を土台に、さらに広い自動化の世界へ踏み込んでいきましょう。皆さんの学習を応援しています。次の動画でお会いしましょう。</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V4企画骨子</t>
         </is>
@@ -3839,238 +3841,238 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>フォーマット統一スキルの設計ポイント（具体的なテンプレートを貼り込む）を実演とともに説明する</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>「曖昧な指示→毎回異なる出力」という問題を具体的に見せてから解決策を提示する</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>実演①：日報作成スキルのSKILL.md作成・テスト・改善を通しで見せる</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>意図通りでない出力もあえて見せて、「改善することで精度が上がる」プロセスを体験させる</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>コードレビュースキルの5観点（動作の正確性・セキュリティ・可読性・パフォーマンス・エラーハンドリング）と優先順位を説明する</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>「最終判断は人間が行う」という重要な注意事項を必ずセットで伝える</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>実演②：コードレビュースキルの作成とテストを実際に行う</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>セキュリティ問題（APIキーのハードコード）が最優先で報告されることを確認する実演を入れる</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>テスト・評価・修正の3ステップ改善サイクルを図解スライドとともに説明する</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>「3回繰り返すと実用的な品質になる」という具体的な目安を伝えて受講者の見通しを持たせる</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>プロンプト記述の3つのコツ（良い例・悪い例の併記、数値基準、禁止事項）を実例つきで説明する</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>各コツに「なぜこれが有効か」の理由を添えて、受講者が自分で応用できるよう理解を深める</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>「最初から完璧を目指さず、動くものを作って磨く」というメッセージを繰り返し伝える</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>完璧主義による挫折を防ぐため、「3回のサイクルで十分実用的」という目標を示す</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>次の動画（V4）でMCPと外部ツール連携を学ぶことをプレビューして継続視聴を促す</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>freeeやブラウザとの連携という具体的な例を挙げて期待感を持たせる</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>スライドとツール画面の切り替えに声の案内を入れる</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>「画面を切り替えます」「スライドに戻ります」を毎回入れて視聴者を迷わせない</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>10分の尺に対して12400〜14000字の増量モード目標を意識した話速・ポーズ配分を調整する</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>実演中に操作の意味を一つひとつ言葉にすることで文字数と情報量を両立させる</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>「コードレビューの観点が思いつかない」というつまずきへの対処を先手で行う</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>5観点を一覧スライドで提示し、「ここから選べばよい」という安心感を与える</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>丁寧語・断定しない表現の一貫性を確認する</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>「〜です」「〜になります」「〜かもしれません」という語調で統一する</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>コードレビュー実演用サンプルコードを事前に準備しておく</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>APIキーのハードコード・エラーハンドリング不足・変数名の不明確さを含むサンプルを用意する</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>全14講師アクション（表情・ジェスチャー・話速・スライド操作・視線等）の演出指示を確認する</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>各sceneのdirectionフィールドに演出指示が記載されていることを最終確認する</t>
         </is>
@@ -4104,139 +4106,139 @@
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>モジュール</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Claude Code講座</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>セクション3-動画4</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>動画タイトル</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>外部ツールと連携する（MCP / freee事例 / ブラウザ操作）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>尺</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>画面収録+標準</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ゴール</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>MCPの概念を理解し、外部ツール（freee、ブラウザ等）との連携を設定できるようになる</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>重要トピック</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>1. MCPの仕組みと役割  2. MCP連携の4カテゴリ  3. freee連携の活用例と設定  4. ブラウザ操作（Playwright CLI / Agent Browser）  5. GUI操作の不安定さと暴走リスクへの注意  6. 段階的な導入の推奨順序</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>受講者のつまずき</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>MCPの概念が抽象的で理解しづらい、設定ファイルの書き方でつまずく、ブラウザ操作の不安定さに戸惑う</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>画面操作方針</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>MCP設定ファイルの編集はエディタをフルスクリーンで収録。freee連携はデモ環境を使った画面収録。ブラウザ操作の実演はゆっくり見せてリスクについても正直に説明する。抽象的な概念の説明はスライドで補足</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>位置付け方針</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>セクション3の締めくくりとして、Claude Codeを「テキスト処理ツール」から「業務全体を横断する自動化プラットフォーム」へ昇華させる可能性を示す。次のセクションへの学習意欲を高める</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>参照一覧</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Claude Code公式のMCP解説、Playwright CLIの仕様、freee MCP連携事例、Agent Browserの概要</t>
         </is>
@@ -4270,216 +4272,216 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>表紙</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>動画タイトルとセクション3-4の導入</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_表紙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>MCPの仕組み図解</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>MCPの役割とMCPサーバーの仕組みを視覚化</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_MCP仕組み</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>MCP連携の4カテゴリ</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>業務系・ブラウザ系・コンテンツ管理系・データベース系を一覧で提示</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2:10</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_4カテゴリ</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>GUI操作のリスクと対策</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>ブラウザ操作の不安定さと暴走リスクへの対処法を整理</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>7:10</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_リスク対策</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>段階的な導入推奨順序</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>読み取り専用→書き込み→複数ツール連携という3段階の流れを図示</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>8:10</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_導入順序</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>セクション3まとめ</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>セクション3全体の学習内容を振り返り、次のセクションへ繋げる</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>9:10</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_まとめ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ツール画面</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>エディタ（MCP設定ファイル）＋freee連携デモ画面</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>mcpServers設定の記述方法とfreeeデータ取得の実演</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>3:00〜7:00</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_ツール画面</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>配布資料</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>MCPサーバー一覧と設定テンプレート</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>主要なMCPサーバーの設定コードをすぐに参照・転用できる資料</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>動画説明欄に配置</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>CC_S3_04_MCP設定テンプレート</t>
         </is>
@@ -4518,17 +4520,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4543,24 +4545,24 @@
           <t>セクション3の最終動画へようこそ。これまでの3本でスラッシュコマンドとAgent Skillsを学び、Claude Codeで定型作業を自動化する力を身につけていただきました。今日はその集大成として、Claude Codeを外部のツールやサービスと連携させる「MCP」という仕組みについてお話しします。</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V4企画骨子</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>0:15</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>今回の動画の概要</t>
         </is>
@@ -4575,24 +4577,24 @@
           <t>これまでのスラッシュコマンドやSkillsは、Claude Codeが自分のPC内のファイルを操作する話でした。MCPを使うと、そこからさらに一歩進んで、freeeのような会計ソフトや、ブラウザ、NotionやJiraなどの外部サービスとも直接連携できるようになります。経費の集計、Webサイトの情報収集、外部サービスへの入力など、これまで手作業でやっていた業務を自動化できる可能性が広がります。ただし、便利な反面、注意が必要な点もあります。特にブラウザ操作については、リスクと対策もしっかりお伝えします。今日も一緒に学んでいきましょう。</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>S3-V4企画骨子（学習ゴール）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>0:50</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4607,24 +4609,24 @@
           <t>まず、MCPとは何かを確認しましょう。</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>1:00</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>2:10</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>MCPの仕組みと役割</t>
         </is>
@@ -4639,24 +4641,24 @@
           <t>MCPとは、Model Context Protocolの略です。Claude Codeと外部のツールやサービスをつなぐ「共通の接続規格」です。少し分かりにくいかもしれませんので、例えで説明します。世界中の電子機器がUSBという規格を通じてつながれるように、Claude CodeもこのMCPという共通規格を通じて、様々な外部サービスとつながることができます。この図をご覧ください。Claude Codeがある左側に、外部サービスがある右側、そしてその間に「MCPサーバー」というプログラムがあります。MCPサーバーはClaude Codeと外部サービスの橋渡し役です。たとえばfreeeと連携したい場合、freee用のMCPサーバーを間に立てることで、Claude Codeがfreeeのデータにアクセスできるようになります。MCP対応のサーバーは、freee・Notion・GitHubなど、多くのサービスで提供されています。MCPサーバーが増えるほどClaude Codeの連携先が広がる、拡張性の高い設計になっています。</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（MCPの仕組み）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2:10</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>2:20</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4671,24 +4673,24 @@
           <t>MCPで連携できるツールのカテゴリを見ていきましょう。</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2:20</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>3:00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>MCP連携の4カテゴリ</t>
         </is>
@@ -4703,24 +4705,24 @@
           <t>MCP連携できるツールは、大きく4つのカテゴリに分かれます。1つめは「業務系ツール」です。freee・Notion・Jiraなど、日常の業務で使うサービスとの連携です。2つめは「ブラウザ操作系」です。Playwright CLIやAgent Browserを使って、Webブラウザの操作を自動化できます。3つめは「コンテンツ管理系」です。WordPress CLIなど、Webサイトのコンテンツ管理と連携できます。4つめは「データベース・ファイル系」です。Google DriveやDropboxなど、クラウドストレージとの連携です。これらを組み合わせることで、Claude Codeはただのテキスト処理ツールから、業務全体を横断する自動化プラットフォームへと進化する可能性があります。今日はこの中から、特に実用性の高い「freee連携」と「ブラウザ操作」について詳しく見ていきます。</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（MCP連携の4カテゴリ）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>3:00</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>3:15</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4735,24 +4737,24 @@
           <t>では、実際にMCPの設定ファイルを見てみましょう。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>3:15</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>実演①：MCP設定ファイルの記述方法</t>
         </is>
@@ -4767,24 +4769,24 @@
           <t>MCPの設定はJSON形式で書きます。Claude Codeの設定ファイルを開いてみます。この「mcpServers」というキーの中に、使いたいMCPサーバーの設定を書きます。構造はこのようになっています。サーバー名、接続方法として起動コマンド、そして認証情報としてAPIキーなどを記述します。たとえばfreee用のMCPサーバーを設定するとします。「freee」というサーバー名の下に、「command」として起動コマンドを書きます。「env」という項目に、freeeのAPIキーを環境変数として設定します。APIキーは直接ここに書くのではなく、環境変数の名前だけを書く形にしてください。実際のAPIキーの値は環境変数として別途設定します。こうすることで、この設定ファイルをGitにコミットしても、APIキーが外部に漏れるリスクを防げます。設定を保存したら、Claude Codeを再起動することで設定が反映されます。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（MCPの仕組み）</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>4:30</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>5:45</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>実演②：freee連携の活用例</t>
         </is>
@@ -4799,24 +4801,24 @@
           <t>次に、freee連携の実際の活用例をご覧ください。freee用のMCPサーバーがセットアップされた状態で、Claude Codeに指示を出します。「今月の経費データを取得して、カテゴリ別に集計してください」と入力します。するとClaude Codeは、MCPサーバーを通じてfreeeのAPIにアクセスします。freeeからデータを取得して、カテゴリ別に集計した結果を表形式で表示してくれました。従来であれば、freeeにログインして、エクスポートボタンを押して、Excelに貼り付けて、集計式を書く、という一連の手順が必要でした。それがClaude Codeへの一言の指示で完了します。「今月の交通費だけ教えて」「先月と今月を比較して」など、自然言語で追加の質問もできます。ただし実際にこれを使うには、freee側でAPIキーを発行する作業と、MCPサーバーのインストール作業が別途必要です。詳細な手順は動画説明欄に配布資料を用意していますので、そちらをご参照ください。</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（freee連携の活用例）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>5:45</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>6:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4831,24 +4833,24 @@
           <t>次に、ブラウザ操作の連携について見てみましょう。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>6:00</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>7:10</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>実演③：ブラウザ操作（Playwright CLI）</t>
         </is>
@@ -4863,24 +4865,24 @@
           <t>ブラウザ操作はPlaywright CLIというMCPサーバーを使います。たとえば「特定のWebサイトから最新のニュースの見出しを10件取得してください」という指示を出します。するとClaude Codeが自動的にブラウザを操作して、指定のWebサイトを開いて、見出しを読み取り、一覧にして返してくれます。情報収集の自動化としては非常に便利です。ただし、ここで正直にお伝えしたいことがあります。ブラウザ操作は、他のMCP連携と比べて不安定なことがあります。Webページのデザインや構造が変わると、突然動かなくなることがあります。今実演してみたところ、このページはうまくいきましたが、別のページでは要素が見つからないエラーが出ることがあります。これはブラウザ自動操作全般に言える特性です。デモとして見ていただくぶんには問題ありませんが、実業務に組み込む際は、この不安定さを踏まえた対策が必要です。</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（GUI操作の不安定さと暴走リスク）</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>7:10</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4895,24 +4897,24 @@
           <t>ブラウザ操作のリスクと対策について、まとめてお伝えします。</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>8:10</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>GUI操作の不安定さと暴走リスクへの注意</t>
         </is>
@@ -4927,24 +4929,24 @@
           <t>ブラウザ操作を含むGUI連携には、2つの主要なリスクがあります。1つめは「動作が不安定になるリスク」です。Webページのデザインや構造が変わると、突然動かなくなることがあります。これはブラウザ操作の宿命のようなものです。2つめは「意図しない操作が実行される暴走リスク」です。これが特に危険です。購入ボタンのクリック、データの削除、重要なフォームへの送信など、取り消しのできない操作が誤って実行されるリスクがあります。対策として3つのことを推奨します。まず「操作範囲を明確に限定する」です。SKILL.mdやプロンプトで、「読み取りのみ」「この画面以外は操作しない」という制約を明確に書きます。次に「テスト環境で十分検証してから本番適用する」です。最後に「重要な操作には人間の確認を挟むルールを設ける」です。AIが操作を提案した時点で一度止めて、人間が確認してから実行するフローにします。この3点を守れば、ブラウザ操作を安全に活用できます。</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（GUI操作の不安定さと暴走リスク）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>8:10</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>8:20</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -4959,24 +4961,24 @@
           <t>MCPを実際に導入するにあたって、推奨する進め方をお伝えします。</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>8:20</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>9:10</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>段階的な導入の推奨順序</t>
         </is>
@@ -4991,24 +4993,24 @@
           <t>MCP連携は非常に魅力的ですが、一度に全部を設定しようとすると混乱します。推奨する導入の順序は3段階です。まず第1段階として「読み取り専用の連携」から始めてください。データの取得、ページの情報読み取りなど、「読む」だけで「書かない」操作です。失敗してもデータが壊れるリスクがありません。安心して試せる第一歩です。次に第2段階として「書き込みを含む連携」へ進みます。ただし「下書き保存」や「メモ追記」など、取り消し可能な操作から始めます。最終的な送信や確定はまだ自動化しません。第3段階として、複数のツールを組み合わせた連携へ進みます。たとえば「freeeからデータを取得して、Notionに集計結果を書き込む」のような複合的な操作です。各段階で、連携が安定して動作することを確認してから次へ進むことが重要です。焦らず積み上げることで、最終的に信頼性の高い自動化が完成します。</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>S3-V4参照情報（段階的な導入の推奨順序）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>9:10</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>切替</t>
         </is>
@@ -5023,24 +5025,24 @@
           <t>では、この動画のまとめをお伝えします。この動画だけでなく、セクション3全体のまとめもお伝えします。</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>S3-V4企画骨子</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>9:20</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>9:45</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>まとめ（動画＋セクション3全体）</t>
         </is>
@@ -5055,24 +5057,24 @@
           <t>今日学んだMCPのポイントをまとめます。MCPはClaude Codeと外部ツールをつなぐ共通の接続規格です。設定はJSONのmcpServersキーで行い、APIキーは環境変数で管理します。freee連携では自然言語の指示だけで経費集計が可能になります。ブラウザ操作は便利ですが不安定さと暴走リスクを認識して使います。導入は読み取り専用から段階的に進めることを推奨します。そしてセクション3全体を振り返ると、動画1でスラッシュコマンド、動画2と3でAgent Skills、そして今日MCPを学びました。これらの武器を手に入れた皆さんは、Claude Codeを単なる質問回答ツールから、自分の業務を自動化してくれるAIアシスタントへと育てる力を持っています。</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>セクション概要、S3-V4参照情報</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>9:45</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>クロージング・次のセクション予告</t>
         </is>
@@ -5087,7 +5089,7 @@
           <t>セクション3、お疲れさまでした。次のセクション4では、これまで学んだ自動化の武器を使って、実際の業務シナリオに沿った応用的な使い方を学んでいきます。これまでの学習で「こんなこともできるのかな」と感じたアイデアを、ぜひ次のセクションで実現していきましょう。皆さんの成長を心からお応援しています。次のセクションでお会いしましょう。</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>セクション概要</t>
         </is>
@@ -5111,238 +5113,238 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>MCPの概念を「USBのような共通接続規格」という具体的な例えで分かりやすく説明する</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>図解スライドでClaude Code・MCPサーバー・外部ツールの3要素の関係を視覚化する</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MCP連携の4カテゴリ（業務系・ブラウザ系・コンテンツ管理系・データベース系）を一覧で提示する</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>「Claude Codeがプラットフォームに変わる可能性」というメッセージで受講者の期待感を高める</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>実演①：MCP設定ファイル（mcpServers）の記述方法を実際に書きながら説明する</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>APIキーは環境変数で管理する理由を明確に伝え、セキュリティ意識を高める</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>実演②：freee連携でデータ取得・集計が自然言語指示で完了する様子をデモで見せる</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>「従来の手順との比較」を対比で見せて、自動化の価値を実感させる</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>実演③：Playwright CLIを使ったブラウザ操作の実演を行い、不安定な部分も正直に見せる</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>不安定さを隠さずに見せることで、受講者が実業務に適用する際の心構えを作る</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>GUI操作の2つのリスク（不安定さ・暴走リスク）と3つの対策を具体例とともに説明する</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>「購入ボタンを誤ってクリック」「データを誤って削除」という具体的な危険シナリオを挙げて警戒を促す</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>段階的な導入推奨順序（読み取り専用→書き込み可→複数ツール連携）を3段階で提示する</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>「焦らず積み上げることで信頼性の高い自動化が完成する」というメッセージを伝える</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>セクション3全体の学習内容を振り返り、受講者の成長を承認して次のセクションへ橋渡しする</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>「スラッシュコマンド・Skills・MCPという3つの武器を手に入れた」という達成感を与える</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>freeeのAPIキー発行とMCPサーバーインストール手順を配布資料で補足する案内を入れる</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>動画内では概要のみ説明し、詳細は説明欄の配布資料に誘導することで動画テンポを維持する</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>スライドとツール画面の切り替えに声の案内を入れる</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>「画面を切り替えます」「スライドに戻ります」を毎回入れて視聴者を迷わせない</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>10分の尺に対して12400〜14000字の増量モード目標を意識した話速・ポーズ配分を調整する</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>実演中に操作の意味を一つひとつ言葉にすることで文字数と情報量を両立させる</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>「MCPの概念が抽象的で分かりにくい」というつまずきへの対処を先手で行う</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>「USBの例え」と「図解スライド」の両方を使い、複数の角度から理解を促す</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>丁寧語・断定しない表現の一貫性を確認する</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>「〜です」「〜になります」「〜かもしれません」という語調で統一する</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>全14講師アクション（表情・ジェスチャー・話速・スライド操作・視線等）の演出指示を確認する</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>各sceneのdirectionフィールドに演出指示が記載されていることを最終確認する</t>
         </is>
